--- a/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
+++ b/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Documents/GitHub/rise-controller/5 - Experimental Data/july_14_2026_water_bottle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A36BA0E8-391C-DA42-A553-50C4BC1819BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9ADDC0-2611-9B45-86AE-4030EA84BD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="18020" windowHeight="20880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="24040" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controls Experiment Results" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>Controller</t>
   </si>
@@ -68,12 +68,6 @@
     <t>cost</t>
   </si>
   <si>
-    <t>tracking error RMS</t>
-  </si>
-  <si>
-    <t>control effort RMS</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -99,6 +93,21 @@
   </si>
   <si>
     <t>LOST</t>
+  </si>
+  <si>
+    <t>Tracking Error RMS</t>
+  </si>
+  <si>
+    <t>Control Effort RMS</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>IntegratedResNet (Developed)</t>
+  </si>
+  <si>
+    <t>NoResNet (Baseline)</t>
   </si>
 </sst>
 </file>
@@ -116,6 +125,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -369,11 +379,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="4" width="4.1640625" customWidth="1"/>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.1640625" customWidth="1"/>
     <col min="5" max="5" width="3.6640625" customWidth="1"/>
     <col min="6" max="6" width="6.1640625" customWidth="1"/>
     <col min="7" max="7" width="7.6640625" customWidth="1"/>
@@ -388,7 +400,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -421,18 +433,18 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -479,7 +491,7 @@
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -526,10 +538,10 @@
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1">
         <v>0.72</v>
@@ -556,10 +568,10 @@
         <v>0.5</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L4" s="1">
         <v>54.294499999999999</v>
@@ -568,12 +580,12 @@
         <v>0.13400000000000001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -603,10 +615,10 @@
         <v>0.01</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L5" s="1">
         <v>67</v>
@@ -620,7 +632,7 @@
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -650,10 +662,10 @@
         <v>0.5</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L6" s="1">
         <v>60.08</v>
@@ -667,7 +679,7 @@
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -712,12 +724,12 @@
         <v>1.9803999999999999</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -764,7 +776,7 @@
     </row>
     <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -806,6 +818,105 @@
         <v>8.5199999999999998E-2</v>
       </c>
       <c r="N9" s="1">
+        <v>2.0699999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.109</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1.5347</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1">
+        <v>0.11550000000000001</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.3765000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.13400000000000001</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1">
+        <v>0.1414</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0.14319999999999999</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1.8535999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8.7099999999999997E-2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1.9803999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="1">
+        <v>9.0399999999999994E-2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>1.8149999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="1">
+        <v>8.5199999999999998E-2</v>
+      </c>
+      <c r="C22" s="1">
         <v>2.0699999999999998</v>
       </c>
     </row>

--- a/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
+++ b/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Documents/GitHub/rise-controller/5 - Experimental Data/july_14_2026_water_bottle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9ADDC0-2611-9B45-86AE-4030EA84BD65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4103099-1243-AE4A-A6E4-563D0A09702C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="24040" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Controls Experiment Results" sheetId="1" r:id="rId1"/>
+    <sheet name="July 14" sheetId="1" r:id="rId1"/>
+    <sheet name="Summaries" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
   <si>
     <t>Controller</t>
   </si>
@@ -108,13 +109,16 @@
   </si>
   <si>
     <t>NoResNet (Baseline)</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -131,6 +135,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -156,11 +167,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -379,7 +393,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -392,10 +406,10 @@
     <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
     <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="55.1640625" customWidth="1"/>
+    <col min="16" max="16" width="55.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,10 +453,13 @@
         <v>21</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -488,8 +505,11 @@
       <c r="N2" s="1">
         <v>1.5347</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O2" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -535,8 +555,11 @@
       <c r="N3" s="1">
         <v>1.3765000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O3" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -582,8 +605,11 @@
       <c r="N4" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O4" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -629,8 +655,11 @@
       <c r="N5" s="1">
         <v>2.11</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O5" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -676,8 +705,11 @@
       <c r="N6" s="1">
         <v>1.8535999999999999</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O6" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
@@ -723,11 +755,14 @@
       <c r="N7" s="1">
         <v>1.9803999999999999</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="O7" s="5">
+        <v>46217</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -773,8 +808,11 @@
       <c r="N8" s="1">
         <v>1.8149999999999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O8" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -820,105 +858,240 @@
       <c r="N9" s="1">
         <v>2.0699999999999998</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="O9" s="5">
+        <v>46217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A001CB-0E61-0544-B3B1-F07FB7C13439}">
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A1" s="6">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="1" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B3" s="4">
         <v>0.109</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C3" s="4">
         <v>1.5347</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="1" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B4" s="4">
         <v>0.11550000000000001</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C4" s="4">
         <v>1.3765000000000001</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="1" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B5" s="4">
         <v>0.13400000000000001</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="1" t="s">
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B6" s="4">
         <v>0.1414</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C6" s="4">
         <v>2.11</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="1" t="s">
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B7" s="4">
         <v>0.14319999999999999</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C7" s="4">
         <v>1.8535999999999999</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B8" s="4">
         <v>8.7099999999999997E-2</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C8" s="4">
         <v>1.9803999999999999</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="1" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B9" s="4">
         <v>9.0399999999999994E-2</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C9" s="4">
         <v>1.8149999999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="1" t="s">
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B10" s="4">
         <v>8.5199999999999998E-2</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C10" s="4">
         <v>2.0699999999999998</v>
       </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
+++ b/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Documents/GitHub/rise-controller/5 - Experimental Data/july_14_2026_water_bottle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4103099-1243-AE4A-A6E4-563D0A09702C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5578C68-963D-B547-AEF5-CE0004DFBFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="24040" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>Controller</t>
   </si>
@@ -75,9 +75,6 @@
     <t>IntegratedResNet</t>
   </si>
   <si>
-    <t>NoResNet</t>
-  </si>
-  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -112,6 +109,12 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Cristian gains</t>
   </si>
 </sst>
 </file>
@@ -147,12 +150,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -167,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -175,6 +184,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,14 +403,12 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.1640625" customWidth="1"/>
-    <col min="5" max="5" width="3.6640625" customWidth="1"/>
+    <col min="3" max="5" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.1640625" customWidth="1"/>
     <col min="7" max="7" width="7.6640625" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
@@ -414,7 +422,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -447,13 +455,13 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>11</v>
@@ -476,15 +484,15 @@
         <v>2.4</v>
       </c>
       <c r="F2" s="2">
-        <f t="shared" ref="F2:F9" si="0">C2*D2+D2*E2+C2*E2+1</f>
+        <f t="shared" ref="F2:F10" si="0">C2*D2+D2*E2+C2*E2+1</f>
         <v>3.0712000000000002</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G9" si="1">C2*D2*E2+C2</f>
+        <f t="shared" ref="G2:G10" si="1">C2*D2*E2+C2</f>
         <v>0.91008</v>
       </c>
       <c r="H2" s="2">
-        <f t="shared" ref="H2:H9" si="2">C2+D2+E2</f>
+        <f t="shared" ref="H2:H10" si="2">C2+D2+E2</f>
         <v>3.23</v>
       </c>
       <c r="I2" s="1">
@@ -561,10 +569,10 @@
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1">
         <v>0.72</v>
@@ -591,10 +599,10 @@
         <v>0.5</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L4" s="1">
         <v>54.294499999999999</v>
@@ -603,7 +611,7 @@
         <v>0.13400000000000001</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O4" s="5">
         <v>46217</v>
@@ -611,7 +619,7 @@
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -641,10 +649,10 @@
         <v>0.01</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L5" s="1">
         <v>67</v>
@@ -661,7 +669,7 @@
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
@@ -691,10 +699,10 @@
         <v>0.5</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L6" s="1">
         <v>60.08</v>
@@ -711,7 +719,7 @@
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
@@ -759,12 +767,12 @@
         <v>46217</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1">
         <v>3</v>
@@ -814,7 +822,7 @@
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -861,6 +869,189 @@
       <c r="O9" s="5">
         <v>46217</v>
       </c>
+    </row>
+    <row r="10" spans="1:16" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="F11" s="2">
+        <f>C11*D11+D11*E11+C11*E11+1</f>
+        <v>9.625</v>
+      </c>
+      <c r="G11" s="2">
+        <f>C11*D11*E11+C11</f>
+        <v>5.375</v>
+      </c>
+      <c r="H11" s="2">
+        <f>C11+D11+E11</f>
+        <v>5.25</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+    </row>
+    <row r="38" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+    </row>
+    <row r="40" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+    </row>
+    <row r="41" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -882,10 +1073,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -903,7 +1094,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="4">
         <v>0.109</v>
@@ -927,7 +1118,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="4">
         <v>0.11550000000000001</v>
@@ -951,13 +1142,13 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4">
         <v>0.13400000000000001</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -975,7 +1166,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4">
         <v>0.1414</v>
@@ -999,7 +1190,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="4">
         <v>0.14319999999999999</v>
@@ -1023,7 +1214,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="4">
         <v>8.7099999999999997E-2</v>
@@ -1047,7 +1238,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>9.0399999999999994E-2</v>
@@ -1071,7 +1262,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="4">
         <v>8.5199999999999998E-2</v>

--- a/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
+++ b/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Documents/GitHub/rise-controller/5 - Experimental Data/july_14_2026_water_bottle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5578C68-963D-B547-AEF5-CE0004DFBFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4690909-6020-3C4A-BCBE-E9E7B81CAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="24040" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="July 14" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
   <si>
     <t>Controller</t>
   </si>
@@ -115,6 +115,9 @@
   </si>
   <si>
     <t>Cristian gains</t>
+  </si>
+  <si>
+    <t>PID</t>
   </si>
 </sst>
 </file>
@@ -412,8 +415,9 @@
     <col min="6" max="6" width="6.1640625" customWidth="1"/>
     <col min="7" max="7" width="7.6640625" customWidth="1"/>
     <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="55.1640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -879,44 +883,98 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
+        <v>1.95</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" ref="F11" si="3">C11*D11+D11*E11+C11*E11+1</f>
+        <v>5.4799000000000007</v>
+      </c>
+      <c r="G11" s="2">
+        <f t="shared" ref="G11" si="4">C11*D11*E11+C11</f>
+        <v>3.11883</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" ref="H11" si="5">C11+D11+E11</f>
+        <v>3.94</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" ref="F12:F13" si="6">C12*D12+D12*E12+C12*E12+1</f>
         <v>1</v>
       </c>
-      <c r="D11" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="F11" s="2">
-        <f>C11*D11+D11*E11+C11*E11+1</f>
-        <v>9.625</v>
-      </c>
-      <c r="G11" s="2">
-        <f>C11*D11*E11+C11</f>
-        <v>5.375</v>
-      </c>
-      <c r="H11" s="2">
-        <f>C11+D11+E11</f>
-        <v>5.25</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="2">
+        <f t="shared" ref="G12:G13" si="7">C12*D12*E12+C12</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" ref="H12:H13" si="8">C12+D12+E12</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="A14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="2">
+        <v>6.64</v>
+      </c>
+      <c r="G14" s="2">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3.51</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F15" s="2"/>
@@ -928,82 +986,106 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
     </row>
-    <row r="17" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
     </row>
-    <row r="18" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
     </row>
-    <row r="19" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
     </row>
-    <row r="21" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
     </row>
-    <row r="22" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
     </row>
-    <row r="24" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-    </row>
-    <row r="25" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="1">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="F24" s="2">
+        <f>C24*D24+D24*E24+C24*E24+1</f>
+        <v>9.625</v>
+      </c>
+      <c r="G24" s="2">
+        <f>C24*D24*E24+C24</f>
+        <v>5.375</v>
+      </c>
+      <c r="H24" s="2">
+        <f>C24+D24+E24</f>
+        <v>5.25</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
     </row>
-    <row r="26" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>

--- a/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
+++ b/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Documents/GitHub/rise-controller/5 - Experimental Data/july_14_2026_water_bottle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4690909-6020-3C4A-BCBE-E9E7B81CAA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA6D8F6-B17E-E34D-B7AC-383AA63EC346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="780" windowWidth="36000" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="July 14" sheetId="1" r:id="rId1"/>
@@ -124,6 +124,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="173" formatCode="0.000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -179,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -188,6 +191,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -488,15 +492,15 @@
         <v>2.4</v>
       </c>
       <c r="F2" s="2">
-        <f t="shared" ref="F2:F10" si="0">C2*D2+D2*E2+C2*E2+1</f>
+        <f t="shared" ref="F2:F9" si="0">C2*D2+D2*E2+C2*E2+1</f>
         <v>3.0712000000000002</v>
       </c>
       <c r="G2" s="2">
-        <f t="shared" ref="G2:G10" si="1">C2*D2*E2+C2</f>
+        <f t="shared" ref="G2:G9" si="1">C2*D2*E2+C2</f>
         <v>0.91008</v>
       </c>
       <c r="H2" s="2">
-        <f t="shared" ref="H2:H10" si="2">C2+D2+E2</f>
+        <f t="shared" ref="H2:H9" si="2">C2+D2+E2</f>
         <v>3.23</v>
       </c>
       <c r="I2" s="1">
@@ -882,75 +886,78 @@
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1">
-        <v>1.95</v>
-      </c>
-      <c r="D11" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1.62</v>
+      <c r="C11">
+        <v>0.50433063830624203</v>
+      </c>
+      <c r="D11">
+        <v>0.18421835424605901</v>
+      </c>
+      <c r="E11">
+        <v>2.5007185421301101</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" ref="F11" si="3">C11*D11+D11*E11+C11*E11+1</f>
-        <v>5.4799000000000007</v>
+        <v>2.8147741930251868</v>
       </c>
       <c r="G11" s="2">
         <f t="shared" ref="G11" si="4">C11*D11*E11+C11</f>
-        <v>3.11883</v>
+        <v>0.73666479633291604</v>
       </c>
       <c r="H11" s="2">
         <f t="shared" ref="H11" si="5">C11+D11+E11</f>
-        <v>3.94</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0.23</v>
+        <v>3.1892675346824113</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0.40736408949806902</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="O11" s="5">
+        <v>46225</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2">
-        <f t="shared" ref="F12:F13" si="6">C12*D12+D12*E12+C12*E12+1</f>
-        <v>1</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2">
-        <f t="shared" ref="G12:G13" si="7">C12*D12*E12+C12</f>
+        <f t="shared" ref="G12:G13" si="6">C12*D12*E12+C12</f>
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" ref="H12:H13" si="8">C12+D12+E12</f>
+        <f t="shared" ref="H12:H13" si="7">C12+D12+E12</f>
         <v>0</v>
       </c>
       <c r="J12" s="1">
         <v>0.2</v>
+      </c>
+      <c r="O12" s="5">
+        <v>46225</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H13" s="2">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
       <c r="J13" s="1">
         <v>1</v>
+      </c>
+      <c r="O13" s="5">
+        <v>46225</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -974,6 +981,9 @@
       </c>
       <c r="H14" s="2">
         <v>3.51</v>
+      </c>
+      <c r="O14" s="5">
+        <v>46225</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
+++ b/5 - Experimental Data/july_14_2026_water_bottle/July 14 2026 Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Documents/GitHub/rise-controller/5 - Experimental Data/july_14_2026_water_bottle/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA6D8F6-B17E-E34D-B7AC-383AA63EC346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2DFE23-F7D2-2D4F-AEDD-C4AE0CEEF8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="780" windowWidth="36000" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="July 14" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="34">
   <si>
     <t>Controller</t>
   </si>
@@ -118,6 +118,24 @@
   </si>
   <si>
     <t>PID</t>
+  </si>
+  <si>
+    <t>30 second run; takeoff from (1.5, 5.5, 0m) to 0.75 altitude</t>
+  </si>
+  <si>
+    <t>deleted</t>
+  </si>
+  <si>
+    <t>60 second run; takeoff from (1.5, 5.5, 0m) to 0.75 altitude</t>
+  </si>
+  <si>
+    <t>traj</t>
+  </si>
+  <si>
+    <t>60 second run; takeoff from (1.5, 0, 0)m to 0.75 altitude</t>
+  </si>
+  <si>
+    <t>60 second run; takeoff from (1.5, 0, 0)m to 0.75 altitude; fans off</t>
   </si>
 </sst>
 </file>
@@ -125,7 +143,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="173" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -182,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -191,7 +209,8 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,72 +429,76 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.1640625" customWidth="1"/>
-    <col min="3" max="5" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" customWidth="1"/>
-    <col min="8" max="8" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="55.1640625" customWidth="1"/>
+    <col min="2" max="2" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+    <col min="4" max="6" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.1640625" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="55.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -483,199 +506,211 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
         <v>0.72</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>0.11</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>2.4</v>
       </c>
-      <c r="F2" s="2">
-        <f t="shared" ref="F2:F9" si="0">C2*D2+D2*E2+C2*E2+1</f>
+      <c r="G2" s="2">
+        <f t="shared" ref="G2:G9" si="0">D2*E2+E2*F2+D2*F2+1</f>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G2" s="2">
-        <f t="shared" ref="G2:G9" si="1">C2*D2*E2+C2</f>
+      <c r="H2" s="2">
+        <f t="shared" ref="H2:H9" si="1">D2*E2*F2+D2</f>
         <v>0.91008</v>
       </c>
-      <c r="H2" s="2">
-        <f t="shared" ref="H2:H9" si="2">C2+D2+E2</f>
+      <c r="I2" s="2">
+        <f t="shared" ref="I2:I9" si="2">D2+E2+F2</f>
         <v>3.23</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>0.5</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>10</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>3</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>41.2761</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0.109</v>
       </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>1.5347</v>
       </c>
-      <c r="O2" s="5">
+      <c r="P2" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>0.72</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>0.11</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>2.4</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <f t="shared" si="0"/>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <f t="shared" si="1"/>
         <v>0.91008</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>0.5</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>15</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>3</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>36.36</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>0.11550000000000001</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>1.3765000000000001</v>
       </c>
-      <c r="O3" s="5">
+      <c r="P3" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>0.72</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>0.11</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>2.4</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <f t="shared" si="0"/>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <f t="shared" si="1"/>
         <v>0.91008</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>0.5</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="K4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="1">
+      <c r="L4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="1">
         <v>54.294499999999999</v>
       </c>
-      <c r="M4" s="1">
+      <c r="N4" s="1">
         <v>0.13400000000000001</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="5">
+      <c r="P4" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>0.25</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>1.3</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>2.9</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <f t="shared" si="0"/>
         <v>5.8199999999999994</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <f t="shared" si="1"/>
         <v>1.1924999999999999</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <f t="shared" si="2"/>
         <v>4.45</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>0.01</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="K5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M5" s="1">
         <v>67</v>
       </c>
-      <c r="M5" s="1">
+      <c r="N5" s="1">
         <v>0.1414</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>2.11</v>
       </c>
-      <c r="O5" s="5">
+      <c r="P5" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -683,49 +718,52 @@
         <v>1</v>
       </c>
       <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
         <v>0.72</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>0.11</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>2.4</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <f t="shared" si="0"/>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <f t="shared" si="1"/>
         <v>0.91008</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>0.5</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="K6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="1">
         <v>60.08</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>0.14319999999999999</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>1.8535999999999999</v>
       </c>
-      <c r="O6" s="5">
+      <c r="P6" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -733,417 +771,837 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1">
         <v>0.72</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>0.11</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>2.4</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <f t="shared" si="0"/>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <f t="shared" si="1"/>
         <v>0.91008</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>0.5</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>10</v>
       </c>
-      <c r="K7" s="1">
-        <v>1</v>
-      </c>
       <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
         <v>56.252499999999998</v>
       </c>
-      <c r="M7" s="1">
+      <c r="N7" s="1">
         <v>8.7099999999999997E-2</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>1.9803999999999999</v>
       </c>
-      <c r="O7" s="5">
+      <c r="P7" s="5">
         <v>46217</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>0.72</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>0.11</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>2.4</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <f t="shared" si="0"/>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <f t="shared" si="1"/>
         <v>0.91008</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>0.5</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>7</v>
       </c>
-      <c r="K8" s="1">
-        <v>1</v>
-      </c>
       <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
         <v>48.6</v>
       </c>
-      <c r="M8" s="1">
+      <c r="N8" s="1">
         <v>9.0399999999999994E-2</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>1.8149999999999999</v>
       </c>
-      <c r="O8" s="5">
+      <c r="P8" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="1">
         <v>0.72</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>0.11</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>2.4</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <f t="shared" si="0"/>
         <v>3.0712000000000002</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <f t="shared" si="1"/>
         <v>0.91008</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <f t="shared" si="2"/>
         <v>3.23</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>0.5</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>10</v>
       </c>
-      <c r="K9" s="1">
-        <v>1</v>
-      </c>
       <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
         <v>61.5</v>
       </c>
-      <c r="M9" s="1">
+      <c r="N9" s="1">
         <v>8.5199999999999998E-2</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>2.0699999999999998</v>
       </c>
-      <c r="O9" s="5">
+      <c r="P9" s="5">
         <v>46217</v>
       </c>
     </row>
-    <row r="10" spans="1:16" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B11" s="1">
         <v>1</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11">
         <v>0.50433063830624203</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.18421835424605901</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>2.5007185421301101</v>
       </c>
-      <c r="F11" s="2">
-        <f t="shared" ref="F11" si="3">C11*D11+D11*E11+C11*E11+1</f>
+      <c r="G11" s="2">
+        <f t="shared" ref="G11" si="3">D11*E11+E11*F11+D11*F11+1</f>
         <v>2.8147741930251868</v>
       </c>
-      <c r="G11" s="2">
-        <f t="shared" ref="G11" si="4">C11*D11*E11+C11</f>
+      <c r="H11" s="2">
+        <f t="shared" ref="H11" si="4">D11*E11*F11+D11</f>
         <v>0.73666479633291604</v>
       </c>
-      <c r="H11" s="2">
-        <f t="shared" ref="H11" si="5">C11+D11+E11</f>
+      <c r="I11" s="2">
+        <f t="shared" ref="I11" si="5">D11+E11+F11</f>
         <v>3.1892675346824113</v>
       </c>
-      <c r="I11" s="8">
+      <c r="J11" s="8">
         <v>0.40736408949806902</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="5">
+      <c r="K11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M11" s="1">
+        <v>50.03</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0.56040000000000001</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2.2069999999999999</v>
+      </c>
+      <c r="P11" s="5">
         <v>46225</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q11" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>0.50433063830624203</v>
+      </c>
+      <c r="E12">
+        <v>0.18421835424605901</v>
+      </c>
+      <c r="F12">
+        <v>2.5007185421301101</v>
+      </c>
+      <c r="G12" s="2">
+        <f t="shared" ref="G12" si="6">D12*E12+E12*F12+D12*F12+1</f>
+        <v>2.8147741930251868</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" ref="H12" si="7">D12*E12*F12+D12</f>
+        <v>0.73666479633291604</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" ref="I12" si="8">D12+E12+F12</f>
+        <v>3.1892675346824113</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0.40736408949806902</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M12" s="1">
+        <v>73.67</v>
+      </c>
+      <c r="N12" s="1">
+        <v>0.39950000000000002</v>
+      </c>
+      <c r="O12" s="1">
+        <v>1.774</v>
+      </c>
+      <c r="P12" s="5">
+        <v>46225</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2">
-        <f t="shared" ref="G12:G13" si="6">C12*D12*E12+C12</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="2">
-        <f t="shared" ref="H12:H13" si="7">C12+D12+E12</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="O12" s="5">
+      <c r="B13" s="1">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0.50433063830624203</v>
+      </c>
+      <c r="E13">
+        <v>0.18421835424605901</v>
+      </c>
+      <c r="F13">
+        <v>2.5007185421301101</v>
+      </c>
+      <c r="G13" s="2">
+        <f t="shared" ref="G13" si="9">D13*E13+E13*F13+D13*F13+1</f>
+        <v>2.8147741930251868</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" ref="H13" si="10">D13*E13*F13+D13</f>
+        <v>0.73666479633291604</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" ref="I13" si="11">D13+E13+F13</f>
+        <v>3.1892675346824113</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0.40736408949806902</v>
+      </c>
+      <c r="K13" s="9">
+        <v>11.349704560043801</v>
+      </c>
+      <c r="L13" s="9">
+        <v>4.6775329483022903</v>
+      </c>
+      <c r="M13" s="1">
+        <v>85.85</v>
+      </c>
+      <c r="N13" s="1">
+        <v>0.40860000000000002</v>
+      </c>
+      <c r="O13" s="1">
+        <v>2.34</v>
+      </c>
+      <c r="P13" s="5">
         <v>46225</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="1" t="s">
+      <c r="Q13" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="2">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5">
+      <c r="B14" s="1">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>0.50433063830624203</v>
+      </c>
+      <c r="E14">
+        <v>0.18421835424605901</v>
+      </c>
+      <c r="F14">
+        <v>2.5007185421301101</v>
+      </c>
+      <c r="G14" s="2">
+        <f t="shared" ref="G14" si="12">D14*E14+E14*F14+D14*F14+1</f>
+        <v>2.8147741930251868</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" ref="H14" si="13">D14*E14*F14+D14</f>
+        <v>0.73666479633291604</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" ref="I14" si="14">D14+E14+F14</f>
+        <v>3.1892675346824113</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0.40736408949806902</v>
+      </c>
+      <c r="K14" s="9">
+        <v>15.156874876043601</v>
+      </c>
+      <c r="L14" s="9">
+        <v>4.9987222477098001</v>
+      </c>
+      <c r="M14" s="1">
+        <v>89.27</v>
+      </c>
+      <c r="N14" s="1">
+        <v>0.4027</v>
+      </c>
+      <c r="O14" s="1">
+        <v>2.3370000000000002</v>
+      </c>
+      <c r="P14" s="5">
         <v>46225</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="1" t="s">
+      <c r="Q14" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="2">
+      <c r="B15" s="1">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="2">
         <v>6.64</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H15" s="2">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I15" s="2">
         <v>3.51</v>
       </c>
-      <c r="O14" s="5">
+      <c r="J15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M15" s="1">
+        <v>319.32</v>
+      </c>
+      <c r="N15" s="1">
+        <v>0.50939999999999996</v>
+      </c>
+      <c r="O15" s="1">
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="P15" s="5">
         <v>46225</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-    </row>
-    <row r="16" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-    </row>
-    <row r="18" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-    </row>
-    <row r="19" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-    </row>
-    <row r="20" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-    </row>
-    <row r="21" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-    </row>
-    <row r="22" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F22" s="2"/>
+      <c r="Q15" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>0.550100802003473</v>
+      </c>
+      <c r="E16">
+        <v>2.66380523805918E-2</v>
+      </c>
+      <c r="F16">
+        <v>2.2266017954239299</v>
+      </c>
+      <c r="G16">
+        <v>6.64</v>
+      </c>
+      <c r="H16">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I16">
+        <v>3.51</v>
+      </c>
+      <c r="J16">
+        <v>0.94352427679622697</v>
+      </c>
+      <c r="K16" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M16" s="1">
+        <v>236.85</v>
+      </c>
+      <c r="N16" s="1">
+        <v>0.32029999999999997</v>
+      </c>
+      <c r="O16" s="1">
+        <v>2.4289999999999998</v>
+      </c>
+      <c r="P16" s="5">
+        <v>46225</v>
+      </c>
+      <c r="Q16" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2</v>
+      </c>
+      <c r="D17">
+        <v>0.550100802003473</v>
+      </c>
+      <c r="E17">
+        <v>2.66380523805918E-2</v>
+      </c>
+      <c r="F17">
+        <v>2.2266017954239299</v>
+      </c>
+      <c r="G17">
+        <v>6.64</v>
+      </c>
+      <c r="H17">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I17">
+        <v>3.51</v>
+      </c>
+      <c r="J17">
+        <v>0.94352427679622697</v>
+      </c>
+      <c r="K17" t="s">
+        <v>13</v>
+      </c>
+      <c r="L17" t="s">
+        <v>13</v>
+      </c>
+      <c r="M17" s="1">
+        <v>289.27999999999997</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0.34849999999999998</v>
+      </c>
+      <c r="O17" s="1">
+        <v>2.6619999999999999</v>
+      </c>
+      <c r="P17" s="5">
+        <v>46225</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>0.550100802003473</v>
+      </c>
+      <c r="E18">
+        <v>2.66380523805918E-2</v>
+      </c>
+      <c r="F18">
+        <v>2.2266017954239299</v>
+      </c>
+      <c r="G18">
+        <v>6.64</v>
+      </c>
+      <c r="H18">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I18">
+        <v>3.51</v>
+      </c>
+      <c r="J18">
+        <v>0.94352427679622697</v>
+      </c>
+      <c r="K18">
+        <v>11.854160901932101</v>
+      </c>
+      <c r="L18">
+        <v>4.90294525847996</v>
+      </c>
+      <c r="M18" s="1">
+        <v>146.85</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0.253</v>
+      </c>
+      <c r="O18" s="1">
+        <v>2.2090000000000001</v>
+      </c>
+      <c r="P18" s="5">
+        <v>46225</v>
+      </c>
+      <c r="Q18" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" s="1">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>0.550100802003473</v>
+      </c>
+      <c r="E19">
+        <v>2.66380523805918E-2</v>
+      </c>
+      <c r="F19">
+        <v>2.2266017954239299</v>
+      </c>
+      <c r="G19">
+        <v>6.64</v>
+      </c>
+      <c r="H19">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="I19">
+        <v>3.51</v>
+      </c>
+      <c r="J19">
+        <v>0.94352427679622697</v>
+      </c>
+      <c r="K19">
+        <v>15.2411607770545</v>
+      </c>
+      <c r="L19">
+        <v>4.9237088985743096</v>
+      </c>
+      <c r="M19" s="1">
+        <v>251.93</v>
+      </c>
+      <c r="N19" s="1">
+        <v>0.30809999999999998</v>
+      </c>
+      <c r="O19" s="1">
+        <v>2.7850000000000001</v>
+      </c>
+      <c r="P19" s="5">
+        <v>46225</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1">
+        <v>2</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20">
+        <v>3.3709550912794999</v>
+      </c>
+      <c r="H20">
+        <v>1.0414817604370299</v>
+      </c>
+      <c r="I20">
+        <v>3.3761902503954802</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="K20" t="s">
+        <v>13</v>
+      </c>
+      <c r="L20" t="s">
+        <v>13</v>
+      </c>
+      <c r="M20" s="1">
+        <v>222.54</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="O20" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="P20" s="5">
+        <v>46225</v>
+      </c>
+      <c r="Q20" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-    </row>
-    <row r="23" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F23" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
-    </row>
-    <row r="24" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="1">
-        <v>1</v>
-      </c>
-      <c r="C24" s="1">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2.5</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="F24" s="2">
-        <f>C24*D24+D24*E24+C24*E24+1</f>
-        <v>9.625</v>
-      </c>
-      <c r="G24" s="2">
-        <f>C24*D24*E24+C24</f>
-        <v>5.375</v>
-      </c>
-      <c r="H24" s="2">
-        <f>C24+D24+E24</f>
-        <v>5.25</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F25" s="2"/>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F27" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="G26" s="2">
+        <f>D26*E26+E26*F26+D26*F26+1</f>
+        <v>9.625</v>
+      </c>
+      <c r="H26" s="2">
+        <f>D26*E26*F26+D26</f>
+        <v>5.375</v>
+      </c>
+      <c r="I26" s="2">
+        <f>D26+E26+F26</f>
+        <v>5.25</v>
+      </c>
+      <c r="Q26" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F28" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F29" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F30" s="2"/>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F31" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F32" s="2"/>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F33" s="2"/>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F34" s="2"/>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F35" s="2"/>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F36" s="2"/>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F37" s="2"/>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-    </row>
-    <row r="38" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F38" s="2"/>
+      <c r="I37" s="2"/>
+    </row>
+    <row r="38" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-    </row>
-    <row r="39" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F39" s="2"/>
+      <c r="I38" s="2"/>
+    </row>
+    <row r="39" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
-    </row>
-    <row r="40" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F40" s="2"/>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-    </row>
-    <row r="41" spans="6:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F41" s="2"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
